--- a/modelo_dashboard_financeiro.xlsx
+++ b/modelo_dashboard_financeiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patri.DESKTOP-0V8P6A5\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3925F9C7-D6F6-422B-8BB7-C2C62836598C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{394E334A-903F-4C67-8E4E-188552642B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16080" yWindow="11190" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="133">
   <si>
     <t>📊 Dashboard Financeiro Pessoal — Modelo de Dados</t>
   </si>
@@ -97,9 +97,6 @@
     <t>GRUPO</t>
   </si>
   <si>
-    <t>Grupo resumido: D.P. | D.T. | D.F. | PGT. | Vend</t>
-  </si>
-  <si>
     <t>GRUPO REAL</t>
   </si>
   <si>
@@ -136,6 +133,9 @@
     <t>Valor previsto/planejado para receber</t>
   </si>
   <si>
+    <t>⚠️  GRUPOS aceitos em DB_DESPESAS → GRUPO e GRUPO REAL:   D.P. (Despesas Pessoais)  |  D.T. (Transporte/Fixas)  |  D.F. (Financeiras)  |  PGT. (Pagamentos)  |  Vend (Vendas/Receitas)</t>
+  </si>
+  <si>
     <t>SUPERMERCADO EXEMPLO LTDA</t>
   </si>
   <si>
@@ -322,6 +322,12 @@
     <t>12/2027</t>
   </si>
   <si>
+    <t>13° 1/2</t>
+  </si>
+  <si>
+    <t>13° 2/2</t>
+  </si>
+  <si>
     <t>FÉRIAS</t>
   </si>
   <si>
@@ -397,7 +403,25 @@
     <t>Internet, celular, telefone fixo</t>
   </si>
   <si>
-    <t>⚠️  GRUPOS aceitos em DB_DESPESAS → GRUPO e GRUPO REAL:   D.P. (Despesas Pessoais)  |  D.T. (Transporte/Fixas)  |  D.F. (Financeiras)</t>
+    <t>PGT. RAYRA</t>
+  </si>
+  <si>
+    <t>PGT.</t>
+  </si>
+  <si>
+    <t>Pagamentos a terceiros / empregados</t>
+  </si>
+  <si>
+    <t>Venda de Ovos</t>
+  </si>
+  <si>
+    <t>Vend</t>
+  </si>
+  <si>
+    <t>Receitas de venda de produtos</t>
+  </si>
+  <si>
+    <t>Grupo resumido: D.P. | D.T. | D.F. |</t>
   </si>
 </sst>
 </file>
@@ -480,7 +504,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -527,6 +551,16 @@
         <fgColor rgb="FFFFF3E0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F7FA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -555,7 +589,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -627,6 +661,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -954,18 +994,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
     </row>
     <row r="2" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
     </row>
     <row r="4" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
@@ -1057,20 +1097,20 @@
         <v>23</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>24</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1083,10 +1123,10 @@
     </row>
     <row r="20" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1094,39 +1134,39 @@
         <v>21</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="23" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="24" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="4" t="s">
+    </row>
+    <row r="26" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="27" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="26" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1186,7 +1226,7 @@
         <v>23</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1915,19 +1955,19 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>21</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1941,10 +1981,10 @@
         <v>92</v>
       </c>
       <c r="D2" s="10">
-        <v>1300</v>
+        <v>5800</v>
       </c>
       <c r="E2" s="10">
-        <v>20000</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2079,7 +2119,7 @@
     </row>
     <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12">
-        <v>46746</v>
+        <v>46726</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>98</v>
@@ -2089,11 +2129,39 @@
       </c>
       <c r="D11" s="20"/>
       <c r="E11" s="14">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8">
+        <v>46741</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" s="20"/>
+      <c r="E12" s="10">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12">
+        <v>46746</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" s="20"/>
+      <c r="E13" s="14">
         <v>5800</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2110,11 +2178,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
+      <c r="B1" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
     </row>
     <row r="2" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="21" t="s">
@@ -2135,7 +2203,7 @@
         <v>42</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2146,7 +2214,7 @@
         <v>42</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2157,7 +2225,7 @@
         <v>42</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2168,7 +2236,7 @@
         <v>42</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2179,7 +2247,7 @@
         <v>42</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2190,51 +2258,51 @@
         <v>42</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="22" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C9" s="22" t="s">
         <v>42</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="22" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C10" s="22" t="s">
         <v>42</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="22" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C11" s="22" t="s">
         <v>42</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="22" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C12" s="22" t="s">
         <v>42</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2245,7 +2313,7 @@
         <v>47</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2256,18 +2324,18 @@
         <v>47</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="23" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C15" s="23" t="s">
         <v>47</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2278,18 +2346,18 @@
         <v>47</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="23" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C17" s="23" t="s">
         <v>47</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2300,7 +2368,7 @@
         <v>55</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2311,11 +2379,31 @@
         <v>55</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:D1"/>
